--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/13/2026, 11:02:46 AM</v>
+        <v>8/27/2026, 12:42:40 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -827,7 +827,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; Cooling_Pump1; DCDC-F; DCDC-R; DD_CAN; DD_Power; DD_Sigs; Dilong_Sigs; Dimmer; EB1; EB2; EC1; F11; F12; F13; F14; F15; F16; F17; F18; F19; F20; F20; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; K18; K19; K20; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; Pumps; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; ShiftConn; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X98; X100; X101; X102; X104; X105; X106; X107; X108; X109; X110; X113; X114; X115; X116; X117; X118; X119; X120; X124; X125; X126; ZombieDisplay</v>
+        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; Cooling_Pump1; DCDC-F; DCDC-R; DD_CAN; DD_Power; DD_Sigs; Dilong_Sigs; Dimmer; EB1; EB2; EC1; F11; F12; F13; F14; F15; F16; F17; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; Pumps; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; ShiftConn; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X98; X100; X101; X102; X104; X105; X106; X107; X108; X109; X110; X113; X114; X115; X116; X117; X118; X119; X120; X124; X125; X126; ZombieDisplay</v>
       </c>
       <c r="B11" t="str">
         <v>connector</v>
@@ -842,7 +842,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G11" t="str">
         <v>ea</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; K19.85_DD_Sigs.11; MG2R.1_Inverter.40</v>
+        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; MG2R.1_Inverter.40; X61_DD_Sigs.11</v>
       </c>
       <c r="B18" t="str">
         <v>wire</v>
@@ -1150,7 +1150,7 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; K19.85_DD_Sigs.11; MG2R.1_Inverter.40</v>
+        <v>Inverter.20_MG1R.1; J1.17_Inverter.35; J1.19_Inverter.14; J1.21_Inverter.3; J1.23_Inverter.23; MG2R.1_Inverter.40; X61_DD_Sigs.11</v>
       </c>
     </row>
     <row r="19">
@@ -1319,7 +1319,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; Bat+.10_K12.30; F20.In_Pumps.1</v>
+        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.10_K12.30</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G23" t="str">
         <v>ea</v>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.7_K18.30; Bat+.8_K19.30; Bat+.9_K20.30; F20.In_Pumps.1</v>
+        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G24" t="str">
         <v>ea</v>
@@ -1396,7 +1396,7 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN; K18.87_F18.IN; K19.87_F19.IN; K20.87_F20.IN</v>
+        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN</v>
       </c>
     </row>
     <row r="25">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" t="str">
         <v>ea</v>
@@ -1478,7 +1478,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61; GndCtrl.2_K18.85</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61</v>
       </c>
     </row>
     <row r="27">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; EB2.+12v_DD_Sigs.1; Net 88; Net 88</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1539,16 +1539,16 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G28" t="str">
         <v>ea</v>
       </c>
       <c r="H28" t="str">
-        <v>18 AWG</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>RD</v>
+        <v>BK</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -1560,12 +1560,12 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>BatCtrl.3_K19.86; BatCtrl.4_K20.86; EB2.+12v_DD_Sigs.1; Net 88</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; K19.85_DD_Sigs.11; K20.85_X102.1; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_Dilong_Sigs.A; PRNDL.3_Dilong_Sigs.A; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
       <c r="B29" t="str">
         <v>wire</v>
@@ -1580,7 +1580,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G29" t="str">
         <v>ea</v>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J29" t="str">
         <v/>
@@ -1601,12 +1601,12 @@
         <v/>
       </c>
       <c r="M29" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; K19.85_DD_Sigs.11; K20.85_X102.1; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_Dilong_Sigs.A; RearDtsch12-M.9_HV- Contactor.Wout</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_Dilong_Sigs.A; PRNDL.3_Dilong_Sigs.A; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_DD_CAN.2; PBCtrl.7_DD_Sigs.4; PBCtrl.7_DD_Sigs.4; PRNDL.4_Dilong_Sigs.G; PRNDL.4_Dilong_Sigs.G; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B30" t="str">
         <v>wire</v>
@@ -1621,7 +1621,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G30" t="str">
         <v>ea</v>
@@ -1630,7 +1630,7 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>WH</v>
+        <v>GN</v>
       </c>
       <c r="J30" t="str">
         <v/>
@@ -1642,12 +1642,12 @@
         <v/>
       </c>
       <c r="M30" t="str">
-        <v>F13.OUT_F12.OUT; FrontDtsch12-F.2_RearDtsch12-F.2; FrontDtsch12-M.9_InDtsch12-F.9; HV+ Contactor.6_InDtsch12-F.8; PRNDL.3_Dilong_Sigs.A; RearDtsch12-M.9_HV- Contactor.Wout</v>
+        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_DD_CAN.2; PBCtrl.7_DD_Sigs.4; PRNDL.4_Dilong_Sigs.G; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_DD_CAN.2; PBCtrl.7_DD_Sigs.4; PBCtrl.7_DD_Sigs.4; PRNDL.4_Dilong_Sigs.G; PRNDL.4_Dilong_Sigs.G; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
       <c r="B31" t="str">
         <v>wire</v>
@@ -1662,7 +1662,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G31" t="str">
         <v>ea</v>
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>GN</v>
+        <v>WHBU</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1683,12 +1683,12 @@
         <v/>
       </c>
       <c r="M31" t="str">
-        <v>BMS-F.4_CanLO.2; CAN.2_CanLO.3; FrontDtsch12-F.10_RearDtsch12-F.10; FrontDtsch12-F.3_RearDtsch12-F.3; FrontDtsch12-M.5_CanLO.1; InDtsch12-F.3_CanLO.4; InDtsch12-M.3_DD_CAN.2; PBCtrl.7_DD_Sigs.4; PRNDL.4_Dilong_Sigs.G; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
       </c>
       <c r="B32" t="str">
         <v>wire</v>
@@ -1703,7 +1703,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="str">
         <v>ea</v>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>WHBU</v>
+        <v>BU</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1724,12 +1724,12 @@
         <v/>
       </c>
       <c r="M32" t="str">
-        <v>FrontDtsch12-F.4_RearDtsch12-F.4</v>
+        <v>FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
       <c r="B33" t="str">
         <v>wire</v>
@@ -1744,7 +1744,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="str">
         <v>ea</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>BU</v>
+        <v>WHBN</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1765,12 +1765,12 @@
         <v/>
       </c>
       <c r="M33" t="str">
-        <v>FrontDtsch12-F.5_RearDtsch12-F.5; MG1R.8_X1.29</v>
+        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DD_Sigs</v>
       </c>
       <c r="B34" t="str">
         <v>wire</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="str">
         <v>ea</v>
@@ -1794,7 +1794,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>WHBN</v>
+        <v>BN</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -1806,12 +1806,12 @@
         <v/>
       </c>
       <c r="M34" t="str">
-        <v>FrontDtsch12-F.6_RearDtsch12-F.6</v>
+        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DD_Sigs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DD_Sigs</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DD_Sigs</v>
       </c>
       <c r="B35" t="str">
         <v>wire</v>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>BN</v>
+        <v>OG</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1847,12 +1847,12 @@
         <v/>
       </c>
       <c r="M35" t="str">
-        <v>FrontDtsch12-F.7_RearDtsch12-F.7; PBCtrl.5_DD_Sigs</v>
+        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DD_Sigs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DD_Sigs</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
       <c r="B36" t="str">
         <v>wire</v>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="str">
         <v>ea</v>
@@ -1876,7 +1876,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>OG</v>
+        <v>WHOG</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1888,12 +1888,12 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v>FrontDtsch12-F.8_RearDtsch12-F.8; PBCtrl.5_DD_Sigs</v>
+        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
       <c r="B37" t="str">
         <v>wire</v>
@@ -1917,7 +1917,7 @@
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>WHOG</v>
+        <v>WHGN</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -1929,12 +1929,12 @@
         <v/>
       </c>
       <c r="M37" t="str">
-        <v>FrontDtsch12-F.9_RearDtsch12-F.9</v>
+        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; MG1R.4_X1.14; PBCtrl.8_DD_Sigs.5; PBCtrl.8_DD_Sigs.5; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
       <c r="B38" t="str">
         <v>wire</v>
@@ -1949,7 +1949,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G38" t="str">
         <v>ea</v>
@@ -1958,7 +1958,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>WHGN</v>
+        <v>RD</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1970,12 +1970,12 @@
         <v/>
       </c>
       <c r="M38" t="str">
-        <v>FrontDtsch12-F.11_RearDtsch12-F.11</v>
+        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; MG1R.4_X1.14; PBCtrl.8_DD_Sigs.5; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MG1R.4_X1.14; PBCtrl.8_DD_Sigs.5; PBCtrl.8_DD_Sigs.5; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
       </c>
       <c r="B39" t="str">
         <v>wire</v>
@@ -1990,16 +1990,16 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G39" t="str">
         <v>ea</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I39" t="str">
-        <v>RD</v>
+        <v>OGRD</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -2011,12 +2011,12 @@
         <v/>
       </c>
       <c r="M39" t="str">
-        <v>FrontBat+.2_Precharge Relay.Coil+; FrontBat+.3_HV+ Contactor.Coil+; FrontBat+.5_HV+ Contactor.5; FrontDtsch12-F.12_RearDtsch12-F.12; FrontDtsch12-M.12_FrontBat+.4; InDtsch12-F.12_FrontBat+.1; InDtsch12-M.12_F15.OUT; J1.15_F11.OUT; K18.86_X100.1; MG1R.4_X1.14; PBCtrl.8_DD_Sigs.5; PWR.Bat+_FrontBat+.6; RearDtsch12-M.12_HV- Contactor.WIn</v>
+        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
       <c r="B40" t="str">
         <v>wire</v>
@@ -2031,16 +2031,16 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40" t="str">
         <v>ea</v>
       </c>
       <c r="H40" t="str">
-        <v>3/0 AWG</v>
+        <v>20 AWG</v>
       </c>
       <c r="I40" t="str">
-        <v>OGRD</v>
+        <v>OG</v>
       </c>
       <c r="J40" t="str">
         <v/>
@@ -2052,12 +2052,12 @@
         <v/>
       </c>
       <c r="M40" t="str">
-        <v>HV DiscRearF.+_X107.1; NET_mnnb3cvb_4; NET_mnnbwso0_7; Pos Fuse.IN_X125.1</v>
+        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
       <c r="B41" t="str">
         <v>wire</v>
@@ -2072,16 +2072,16 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="str">
         <v>ea</v>
       </c>
       <c r="H41" t="str">
-        <v>20 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I41" t="str">
-        <v>OG</v>
+        <v>OGRD</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2093,12 +2093,12 @@
         <v/>
       </c>
       <c r="M41" t="str">
-        <v>NET_mnnb3cvb_4; NET_mnnbwso0_7</v>
+        <v>NET_mnnb3cvb_4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
       <c r="B42" t="str">
         <v>wire</v>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="str">
         <v>ea</v>
       </c>
       <c r="H42" t="str">
-        <v>14 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I42" t="str">
         <v>OGRD</v>
@@ -2134,12 +2134,12 @@
         <v/>
       </c>
       <c r="M42" t="str">
-        <v>NET_mnnb3cvb_4</v>
+        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B43" t="str">
         <v>wire</v>
@@ -2154,16 +2154,16 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="str">
         <v>ea</v>
       </c>
       <c r="H43" t="str">
-        <v>16 AWG</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>OGRD</v>
+        <v>OGBK</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2175,12 +2175,12 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>NET_mnnbwso0_7; Precharge Resistor.1_Precharge Relay.COM</v>
+        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
       <c r="B44" t="str">
         <v>wire</v>
@@ -2195,13 +2195,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="str">
         <v>ea</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>3/0 AWG</v>
       </c>
       <c r="I44" t="str">
         <v>OGBK</v>
@@ -2216,12 +2216,12 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>HV DiscFrontF.+_X126.1; HV DiscRearM.-_HV DiscFrontM.-; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
       <c r="B45" t="str">
         <v>wire</v>
@@ -2236,16 +2236,16 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45" t="str">
         <v>ea</v>
       </c>
       <c r="H45" t="str">
-        <v>3/0 AWG</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>OGBK</v>
+        <v>WHRD</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2257,12 +2257,12 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>HV DiscRearF.-_X106.1; HV- Contactor.COM_X87.1; HV- Contactor.NO_X88.1; Inverter HV.HV-_HV DiscFrontF.-</v>
+        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
       <c r="B46" t="str">
         <v>wire</v>
@@ -2286,7 +2286,7 @@
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>WHRD</v>
+        <v>RDWH</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2298,12 +2298,12 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>BMS-F.1_DCDC-F.4; BMS-R.1_DCDC-R.4</v>
+        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DD_Sigs.6_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_DD_CAN.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
       <c r="B47" t="str">
         <v>wire</v>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G47" t="str">
         <v>ea</v>
@@ -2327,7 +2327,7 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>RDWH</v>
+        <v>YE</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2339,12 +2339,12 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>BMS-F.2_DCDC-F.3; BMS-R.2_DCDC-R.3</v>
+        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DD_Sigs.6_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_DD_CAN.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DD_Sigs.6_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_DD_CAN.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>Gnd.1_DD_Sigs.2; OilPump.6_X1.30</v>
       </c>
       <c r="B48" t="str">
         <v>wire</v>
@@ -2359,16 +2359,16 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G48" t="str">
         <v>ea</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>12 AWG</v>
       </c>
       <c r="I48" t="str">
-        <v>YE</v>
+        <v>BK</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2380,12 +2380,12 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>BMS-F.3_CanHI.2; CAN.1_CanHI.3; DD_Sigs.6_Dimmer.Signal; FrontDtsch12-M.4_CanHI.1; InDtsch12-F.2_CanHI.4; InDtsch12-M.2_DD_CAN.1; Term.1_RearDtsch12-M.4; Term.2_RearDtsch12-M.5</v>
+        <v>Gnd.1_DD_Sigs.2; OilPump.6_X1.30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Gnd.1_DD_Sigs.2; OilPump.6_X1.30</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
       <c r="B49" t="str">
         <v>wire</v>
@@ -2400,16 +2400,16 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="str">
         <v>ea</v>
       </c>
       <c r="H49" t="str">
-        <v>12 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I49" t="str">
-        <v>BK</v>
+        <v>WH</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2421,12 +2421,12 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>Gnd.1_DD_Sigs.2; OilPump.6_X1.30</v>
+        <v>PBCtrl.1_Caliper.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
       <c r="B50" t="str">
         <v>wire</v>
@@ -2450,7 +2450,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I50" t="str">
-        <v>WH</v>
+        <v>YE</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2462,12 +2462,12 @@
         <v/>
       </c>
       <c r="M50" t="str">
-        <v>PBCtrl.1_Caliper.1</v>
+        <v>PBCtrl.2_Caliper.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
       <c r="B51" t="str">
         <v>wire</v>
@@ -2491,7 +2491,7 @@
         <v>14 AWG</v>
       </c>
       <c r="I51" t="str">
-        <v>YE</v>
+        <v>BK</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2503,12 +2503,12 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>PBCtrl.2_Caliper.2</v>
+        <v>PBCtrl.3_X98.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K12.86_X117.1; K17.86_X110.1</v>
       </c>
       <c r="B52" t="str">
         <v>wire</v>
@@ -2523,16 +2523,16 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G52" t="str">
         <v>ea</v>
       </c>
       <c r="H52" t="str">
-        <v>14 AWG</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>BK</v>
+        <v>VT</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2544,12 +2544,12 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>PBCtrl.3_X98.1</v>
+        <v>CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K17.86_X110.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K12.86_X117.1; K17.86_X110.1</v>
+        <v>PBCtrl.3_X98.1; RearDtsch12-M.1_PWR.Gnd</v>
       </c>
       <c r="B53" t="str">
         <v>wire</v>
@@ -2564,16 +2564,16 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G53" t="str">
         <v>ea</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>20 AWG</v>
       </c>
       <c r="I53" t="str">
-        <v>VT</v>
+        <v>BK</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2585,12 +2585,12 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K17.86_X110.1</v>
+        <v>PBCtrl.3_X98.1; RearDtsch12-M.1_PWR.Gnd</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PBCtrl.3_X98.1; RearDtsch12-M.1_PWR.Gnd</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
       <c r="B54" t="str">
         <v>wire</v>
@@ -2605,16 +2605,16 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="str">
         <v>ea</v>
       </c>
       <c r="H54" t="str">
-        <v>20 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I54" t="str">
-        <v>BK</v>
+        <v>GNBU</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2626,12 +2626,12 @@
         <v/>
       </c>
       <c r="M54" t="str">
-        <v>PBCtrl.3_X98.1; RearDtsch12-M.1_PWR.Gnd</v>
+        <v>CtrlRelay.4_EC1.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
       <c r="B55" t="str">
         <v>wire</v>
@@ -2652,10 +2652,10 @@
         <v>ea</v>
       </c>
       <c r="H55" t="str">
-        <v>14 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I55" t="str">
-        <v>GNBU</v>
+        <v>GNBK</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2667,12 +2667,12 @@
         <v/>
       </c>
       <c r="M55" t="str">
-        <v>CtrlRelay.4_EC1.2</v>
+        <v>CtrlRelay.10_EC1.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
       <c r="B56" t="str">
         <v>wire</v>
@@ -2693,10 +2693,10 @@
         <v>ea</v>
       </c>
       <c r="H56" t="str">
-        <v>16 AWG</v>
+        <v>14 AWG</v>
       </c>
       <c r="I56" t="str">
-        <v>GNBK</v>
+        <v>GN</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2708,12 +2708,12 @@
         <v/>
       </c>
       <c r="M56" t="str">
-        <v>CtrlRelay.10_EC1.5</v>
+        <v>CtrlRelay.1_EC1.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
       <c r="B57" t="str">
         <v>wire</v>
@@ -2734,10 +2734,10 @@
         <v>ea</v>
       </c>
       <c r="H57" t="str">
-        <v>14 AWG</v>
+        <v>16 AWG</v>
       </c>
       <c r="I57" t="str">
-        <v>GN</v>
+        <v>GNYE</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2749,12 +2749,12 @@
         <v/>
       </c>
       <c r="M57" t="str">
-        <v>CtrlRelay.1_EC1.3</v>
+        <v>CtrlRelay.5_EC1.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
       </c>
       <c r="B58" t="str">
         <v>wire</v>
@@ -2769,16 +2769,16 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="str">
         <v>ea</v>
       </c>
       <c r="H58" t="str">
-        <v>16 AWG</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v>GNYE</v>
+        <v>WHBK</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2790,12 +2790,12 @@
         <v/>
       </c>
       <c r="M58" t="str">
-        <v>CtrlRelay.5_EC1.6</v>
+        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
+        <v>CDLSw.1_CtrlRelay.7</v>
       </c>
       <c r="B59" t="str">
         <v>wire</v>
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" t="str">
         <v>ea</v>
@@ -2819,7 +2819,7 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>WHBK</v>
+        <v>BKRD</v>
       </c>
       <c r="J59" t="str">
         <v/>
@@ -2831,12 +2831,12 @@
         <v/>
       </c>
       <c r="M59" t="str">
-        <v>EC1.4_CDLLED.2; Gnd.2_X114.1</v>
+        <v>CDLSw.1_CtrlRelay.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
       </c>
       <c r="B60" t="str">
         <v>wire</v>
@@ -2860,7 +2860,7 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>BKRD</v>
+        <v>OGRD</v>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2872,12 +2872,12 @@
         <v/>
       </c>
       <c r="M60" t="str">
-        <v>CDLSw.1_CtrlRelay.7</v>
+        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+        <v>DD_Sigs.9_EB2.VSS</v>
       </c>
       <c r="B61" t="str">
         <v>wire</v>
@@ -2901,7 +2901,7 @@
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>OGRD</v>
+        <v>GNRD</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2913,12 +2913,12 @@
         <v/>
       </c>
       <c r="M61" t="str">
-        <v>HV DiscRearM.+_HV DiscFrontM.+</v>
+        <v>DD_Sigs.9_EB2.VSS</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DD_Sigs.9_EB2.VSS</v>
+        <v>EB2.+12v_DD_Sigs.1</v>
       </c>
       <c r="B62" t="str">
         <v>wire</v>
@@ -2942,7 +2942,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>GNRD</v>
+        <v>BKWH</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -2954,12 +2954,12 @@
         <v/>
       </c>
       <c r="M62" t="str">
-        <v>DD_Sigs.9_EB2.VSS</v>
+        <v>EB2.+12v_DD_Sigs.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>EB2.+12v_DD_Sigs.1</v>
+        <v>MG2R.8_X1.13</v>
       </c>
       <c r="B63" t="str">
         <v>wire</v>
@@ -2983,7 +2983,7 @@
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>BKWH</v>
+        <v>GY</v>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -2995,12 +2995,12 @@
         <v/>
       </c>
       <c r="M63" t="str">
-        <v>EB2.+12v_DD_Sigs.1</v>
+        <v>MG2R.8_X1.13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>MG2R.8_X1.13</v>
+        <v>MG2R.4_X1.12</v>
       </c>
       <c r="B64" t="str">
         <v>wire</v>
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v>GY</v>
+        <v>LI</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3036,12 +3036,12 @@
         <v/>
       </c>
       <c r="M64" t="str">
-        <v>MG2R.8_X1.13</v>
+        <v>MG2R.4_X1.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>MG2R.4_X1.12</v>
+        <v>ShiftConn.8_X124.1</v>
       </c>
       <c r="B65" t="str">
         <v>wire</v>
@@ -3062,10 +3062,10 @@
         <v>ea</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>20 AWG</v>
       </c>
       <c r="I65" t="str">
-        <v>LI</v>
+        <v>RD</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3077,12 +3077,12 @@
         <v/>
       </c>
       <c r="M65" t="str">
-        <v>MG2R.4_X1.12</v>
+        <v>ShiftConn.8_X124.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ShiftConn.8_X124.1</v>
+        <v>ShiftConn.3_Inverter.25</v>
       </c>
       <c r="B66" t="str">
         <v>wire</v>
@@ -3103,10 +3103,10 @@
         <v>ea</v>
       </c>
       <c r="H66" t="str">
-        <v>20 AWG</v>
+        <v/>
       </c>
       <c r="I66" t="str">
-        <v>RD</v>
+        <v>YEOG</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3118,12 +3118,12 @@
         <v/>
       </c>
       <c r="M66" t="str">
-        <v>ShiftConn.8_X124.1</v>
+        <v>ShiftConn.3_Inverter.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ShiftConn.3_Inverter.25</v>
+        <v>EB2.+12v_DD_Sigs.1; Net 79; Net 79</v>
       </c>
       <c r="B67" t="str">
         <v>wire</v>
@@ -3138,16 +3138,16 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="str">
         <v>ea</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>18 AWG</v>
       </c>
       <c r="I67" t="str">
-        <v>YEOG</v>
+        <v>RD</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3159,7 +3159,7 @@
         <v/>
       </c>
       <c r="M67" t="str">
-        <v>ShiftConn.3_Inverter.25</v>
+        <v>EB2.+12v_DD_Sigs.1; Net 79</v>
       </c>
     </row>
     <row r="68">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Net 166</v>
+        <v>Net 154</v>
       </c>
       <c r="B70" t="str">
         <v>wire</v>
@@ -3282,12 +3282,12 @@
         <v/>
       </c>
       <c r="M70" t="str">
-        <v>Net 166</v>
+        <v>Net 154</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Net 167; Net 168</v>
+        <v>Net 155; Net 156</v>
       </c>
       <c r="B71" t="str">
         <v>wire</v>
@@ -3323,7 +3323,7 @@
         <v/>
       </c>
       <c r="M71" t="str">
-        <v>Net 167; Net 168</v>
+        <v>Net 155; Net 156</v>
       </c>
     </row>
     <row r="72">
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/27/2026, 12:42:40 PM</v>
+        <v>8/27/2026, 12:54:05 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/27/2026, 12:54:05 PM</v>
+        <v>8/28/2026, 12:21:18 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 12:21:18 PM</v>
+        <v>8/28/2026, 1:18:36 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 1:18:36 PM</v>
+        <v>8/28/2026, 1:35:38 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 1:35:38 PM</v>
+        <v>8/28/2026, 1:45:44 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 1:45:44 PM</v>
+        <v>8/28/2026, 2:03:46 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 2:03:46 PM</v>
+        <v>8/28/2026, 2:08:20 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 2:08:20 PM</v>
+        <v>8/28/2026, 2:20:39 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/28/2026, 2:20:39 PM</v>
+        <v>8/29/2026, 11:22:47 AM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3527,7 +3527,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/29/2026, 11:22:47 AM</v>
+        <v>8/29/2026, 11:27:48 AM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -827,7 +827,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Bat+; BatCtrl; BMS-F; BMS-R; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; Cooling_Pump1; DCDC-F; DCDC-R; DD_CAN; DD_Power; DD_Sigs; Dilong_Sigs; Dimmer; EB1; EB2; EC1; F11; F12; F13; F14; F15; F16; F17; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GndCtrl; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K11; K12; K13; K14; K15; K16; K17; MgRideL; MgRideR; Neg Fuse; OilPump; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; Pumps; PWR; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; Sense1; Sense2; Sense3; ShiftConn; Term; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X57; X58; X59; X61; X62; X63; X64; X65; X67; X71; X72; X73; X74; X75; X76; X77; X82; X85; X86; X87; X88; X93; X98; X100; X101; X102; X104; X105; X106; X107; X108; X109; X110; X113; X114; X115; X116; X117; X118; X119; X120; X124; X125; X126; ZombieDisplay</v>
+        <v>Bat+; BMS-F; BMS-R; Brake Lights; Caliper; CAN; CanHI; CanLO; CDLLED; CDLSw; Chassis; Cooling_Pump1; DCDC-F; DCDC-R; DD_CAN; DD_Power; DD_Sigs; Dilong_Sigs; Dimmer; EB1; EB2; EC1; F11; F12; F13; F14; F15; F16; F17; F21; F23; FrontBat+; FrontDtsch12-F; FrontDtsch12-M; Gnd; GrnLed; HV Bat Front; HV Bat Rear; HV DiscFrontF; HV DiscFrontM; HV DiscRearF; HV DiscRearM; HV- Contactor; HV+ Contactor; IGN+; InDtsch12-F; InDtsch12-M; Inverter HV; K; L; M; MgRideL; MgRideR; N; Neg Fuse; O; OilPump; P; PBCtrl; PkBrk; Pos Fuse; Precharge Relay; Precharge Resistor; PRNDL; Pumps; PWR; R; RearDtsch12-F; RearDtsch12-M; RedLed; RT32; RT33; RT35; RT38; S; Sense1; Sense2; Sense3; ShiftConn; sw12; T; Term; Trans Park-Pawl (HSDN); U; X46; X47; X48; X49; X50; X51; X52; X53; X54; X55; X61; X62; X63; X64; X65; X71; X72; X73; X74; X75; X77; X82; X85; X86; X87; X88; X93; X98; X100; X101; X102; X104; X105; X106; X107; X108; X109; X110; X113; X114; X115; X116; X117; X118; X119; X120; X124; X125; X126; ZombieDisplay</v>
       </c>
       <c r="B11" t="str">
         <v>connector</v>
@@ -842,7 +842,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G11" t="str">
         <v>ea</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; K12.85_X120.1; K12.85_X120.1; K12.86_X117.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
+        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; M.85_X120.1; M.85_X120.1; M.86_X117.1; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42; X3.10_X1.41; X3.12_X1.40</v>
       </c>
       <c r="B16" t="str">
         <v>wire</v>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; K12.85_X120.1; K12.86_X117.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
+        <v>CtrlRelay.3_EB2.+12V; InDtsch12-M.5_X1.4; InDtsch12-M.6_X1.34; InDtsch12-M.7_X1.33; J1.39_X3.7; M.85_X120.1; M.86_X117.1; X3.10_X1.41; X3.12_X1.40; X3.3_X1.37; X3.8_X1.38; X3.9_X1.42</v>
       </c>
     </row>
     <row r="17">
@@ -1319,7 +1319,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30; Bat+.10_K12.30</v>
+        <v>Bat+.1_S.30; Bat+.2_T.30; Bat+.3_L.30; Bat+.4_U.30; Bat+.5_O.30; Bat+.6_N.30; Bat+.10_M.30</v>
       </c>
       <c r="B23" t="str">
         <v>wire</v>
@@ -1355,12 +1355,12 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>Bat+.10_K12.30; Bat+.1_K11.30; Bat+.2_K13.30; Bat+.3_K14.30; Bat+.4_K15.30; Bat+.5_K16.30; Bat+.6_K17.30</v>
+        <v>Bat+.10_M.30; Bat+.1_S.30; Bat+.2_T.30; Bat+.3_L.30; Bat+.4_U.30; Bat+.5_O.30; Bat+.6_N.30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN</v>
+        <v>L.87_F14.IN; N.87_F17.IN; O.87_F16.IN; S.87_F11.IN; T.87_F13.IN; U.87_F15.IN</v>
       </c>
       <c r="B24" t="str">
         <v>wire</v>
@@ -1396,12 +1396,12 @@
         <v/>
       </c>
       <c r="M24" t="str">
-        <v>K11.87_F11.IN; K13.87_F13.IN; K14.87_F14.IN; K15.87_F15.IN; K16.87_F16.IN; K17.87_F17.IN</v>
+        <v>L.87_F14.IN; N.87_F17.IN; O.87_F16.IN; S.87_F11.IN; T.87_F13.IN; U.87_F15.IN</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>IGN+.1_S.86; IGN+.2_T.86; IGN+.3_L.86; IGN+.4_U.86; IGN+.5_O.86</v>
       </c>
       <c r="B25" t="str">
         <v>wire</v>
@@ -1437,12 +1437,12 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>IGN+.1_K11.86; IGN+.2_K13.86; IGN+.3_K14.86; IGN+.4_K15.86; IGN+.5_K16.86</v>
+        <v>IGN+.1_S.86; IGN+.2_T.86; IGN+.3_L.86; IGN+.4_U.86; IGN+.5_O.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_L.85; Gnd.4_U.85; Gnd.5_X61</v>
       </c>
       <c r="B26" t="str">
         <v>wire</v>
@@ -1478,12 +1478,12 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_K14.85; Gnd.4_K15.85; Gnd.5_X61</v>
+        <v>FrontDtsch12-M.1_DCDC-F.1; Gnd.1_DD_Sigs.2; Gnd.2_X114.1; Gnd.3_L.85; Gnd.4_U.85; Gnd.5_X61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bat+.1_K11.30; F13.OUT_F12.OUT; K12.87_F12.IN</v>
+        <v>Bat+.1_S.30; F13.OUT_F12.OUT; M.87_F12.IN</v>
       </c>
       <c r="B27" t="str">
         <v>wire</v>
@@ -1519,12 +1519,12 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>Bat+.1_K11.30; F13.OUT_F12.OUT; K12.87_F12.IN</v>
+        <v>Bat+.1_S.30; F13.OUT_F12.OUT; M.87_F12.IN</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; M.85_X120.1; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
       <c r="B28" t="str">
         <v>wire</v>
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; K12.85_X120.1; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
+        <v>CDLSw.3_CtrlRelay.9; FrontDtsch12-F.1_RearDtsch12-F.1; FrontDtsch12-M.7_InDtsch12-F.5; Gnd.1_DD_Sigs.2; Gnd.5_X61; HV+ Contactor.Coil-_InDtsch12-F.7; InDtsch12-M.1_X104.1; M.85_X120.1; PBCtrl.6_PkBrk.2; Precharge Relay.Coil-_InDtsch12-F.6; RearDtsch12-M.1_PWR.Gnd; RearDtsch12-M.7_HV- Contactor.Coil-</v>
       </c>
     </row>
     <row r="29">
@@ -2508,7 +2508,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K12.86_X117.1; K17.86_X110.1</v>
+        <v>CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; M.86_X117.1; M.86_X117.1; N.86_X110.1</v>
       </c>
       <c r="B52" t="str">
         <v>wire</v>
@@ -2544,7 +2544,7 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; K12.86_X117.1; K17.86_X110.1</v>
+        <v>CtrlRelay.3_EB2.+12V; F14.OUT_PBCtrl.4; F21.In_IGN+.10; F23.IN_X105.1; M.86_X117.1; N.86_X110.1</v>
       </c>
     </row>
     <row r="53">
@@ -3041,7 +3041,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ShiftConn.8_X124.1</v>
+        <v>ShiftConn.8_X124.1; sw12.1_Trans Park-Pawl (HSDN).B</v>
       </c>
       <c r="B65" t="str">
         <v>wire</v>
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="str">
         <v>ea</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="M65" t="str">
-        <v>ShiftConn.8_X124.1</v>
+        <v>ShiftConn.8_X124.1; sw12.1_Trans Park-Pawl (HSDN).B</v>
       </c>
     </row>
     <row r="66">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Net 154</v>
+        <v>Net 156</v>
       </c>
       <c r="B70" t="str">
         <v>wire</v>
@@ -3282,12 +3282,12 @@
         <v/>
       </c>
       <c r="M70" t="str">
-        <v>Net 154</v>
+        <v>Net 156</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Net 155; Net 156</v>
+        <v>Net 157; Net 158</v>
       </c>
       <c r="B71" t="str">
         <v>wire</v>
@@ -3323,7 +3323,7 @@
         <v/>
       </c>
       <c r="M71" t="str">
-        <v>Net 155; Net 156</v>
+        <v>Net 157; Net 158</v>
       </c>
     </row>
     <row r="72">
@@ -3410,48 +3410,89 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
+        <v>X1.31_Brake Lights.1; X1.50_Trans Park-Pawl (HSDN).PawlOut</v>
+      </c>
+      <c r="B74" t="str">
+        <v>wire</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Unassigned</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>2</v>
+      </c>
+      <c r="G74" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H74" t="str">
+        <v>20 AWG</v>
+      </c>
+      <c r="I74" t="str">
+        <v>WH</v>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v>X1.31_Brake Lights.1; X1.50_Trans Park-Pawl (HSDN).PawlOut</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>10863985</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B75" t="str">
         <v>contact</v>
       </c>
-      <c r="C74" t="str">
+      <c r="C75" t="str">
         <v>10863985</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D75" t="str">
         <v>Aptiv</v>
       </c>
-      <c r="E74" t="str">
-        <v/>
-      </c>
-      <c r="F74" t="str">
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
         <v>33</v>
       </c>
-      <c r="G74" t="str">
-        <v>ea</v>
-      </c>
-      <c r="H74" t="str">
-        <v/>
-      </c>
-      <c r="I74" t="str">
-        <v/>
-      </c>
-      <c r="J74" t="str">
-        <v/>
-      </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
-      <c r="M74" t="str">
+      <c r="G75" t="str">
+        <v>ea</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M75"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3511,7 +3552,7 @@
         <v>Total Wires</v>
       </c>
       <c r="B9">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -3527,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/29/2026, 11:27:48 AM</v>
+        <v>8/29/2026, 12:46:10 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/29/2026, 12:46:10 PM</v>
+        <v>8/30/2026, 6:03:55 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/30/2026, 6:03:55 PM</v>
+        <v>8/30/2026, 6:17:50 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/30/2026, 6:17:50 PM</v>
+        <v>8/30/2026, 7:30:40 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/30/2026, 7:30:40 PM</v>
+        <v>8/30/2026, 7:33:43 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/30/2026, 7:33:43 PM</v>
+        <v>8/30/2026, 7:49:44 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>8/30/2026, 7:49:44 PM</v>
+        <v>9/1/2026, 11:54:56 AM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/1/2026, 11:54:56 AM</v>
+        <v>9/1/2026, 5:51:44 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/1/2026, 5:51:44 PM</v>
+        <v>9/2/2026, 12:40:26 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/2/2026, 12:40:26 PM</v>
+        <v>9/2/2026, 12:58:22 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/2/2026, 12:58:22 PM</v>
+        <v>9/2/2026, 1:59:03 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/2/2026, 1:59:03 PM</v>
+        <v>9/2/2026, 2:04:29 PM</v>
       </c>
     </row>
   </sheetData>

--- a/rendered/evj-55.plan_bom.xlsx
+++ b/rendered/evj-55.plan_bom.xlsx
@@ -3568,7 +3568,7 @@
         <v>Generated</v>
       </c>
       <c r="B12" t="str">
-        <v>9/2/2026, 2:04:29 PM</v>
+        <v>9/2/2026, 3:34:49 PM</v>
       </c>
     </row>
   </sheetData>
